--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -2461,7 +2461,7 @@
         <v>136472418</v>
       </c>
       <c r="B17" t="n">
-        <v>92513</v>
+        <v>92516</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136472416</v>
       </c>
       <c r="B49" t="n">
-        <v>111636</v>
+        <v>111643</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>136472421</v>
       </c>
       <c r="B54" t="n">
-        <v>99365</v>
+        <v>99368</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>136472417</v>
       </c>
       <c r="B98" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>136472419</v>
       </c>
       <c r="B99" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>136472413</v>
       </c>
       <c r="B119" t="n">
-        <v>98210</v>
+        <v>98213</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -2461,7 +2461,7 @@
         <v>136472418</v>
       </c>
       <c r="B17" t="n">
-        <v>92516</v>
+        <v>92517</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136472416</v>
       </c>
       <c r="B49" t="n">
-        <v>111643</v>
+        <v>111644</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>136472421</v>
       </c>
       <c r="B54" t="n">
-        <v>99368</v>
+        <v>99369</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>136472417</v>
       </c>
       <c r="B98" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>136472419</v>
       </c>
       <c r="B99" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>136472413</v>
       </c>
       <c r="B119" t="n">
-        <v>98213</v>
+        <v>98214</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -2461,7 +2461,7 @@
         <v>136472418</v>
       </c>
       <c r="B17" t="n">
-        <v>92517</v>
+        <v>92522</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136472416</v>
       </c>
       <c r="B49" t="n">
-        <v>111644</v>
+        <v>111649</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>136472421</v>
       </c>
       <c r="B54" t="n">
-        <v>99369</v>
+        <v>99374</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>136472417</v>
       </c>
       <c r="B98" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>136472419</v>
       </c>
       <c r="B99" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>136472413</v>
       </c>
       <c r="B119" t="n">
-        <v>98214</v>
+        <v>98219</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -2461,7 +2461,7 @@
         <v>136472418</v>
       </c>
       <c r="B17" t="n">
-        <v>92522</v>
+        <v>92524</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136472416</v>
       </c>
       <c r="B49" t="n">
-        <v>111649</v>
+        <v>111651</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>136472421</v>
       </c>
       <c r="B54" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>136472417</v>
       </c>
       <c r="B98" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>136472419</v>
       </c>
       <c r="B99" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>136472413</v>
       </c>
       <c r="B119" t="n">
-        <v>98219</v>
+        <v>98221</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -2461,7 +2461,7 @@
         <v>136472418</v>
       </c>
       <c r="B17" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136472416</v>
       </c>
       <c r="B49" t="n">
-        <v>111651</v>
+        <v>111657</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>136472421</v>
       </c>
       <c r="B54" t="n">
-        <v>99376</v>
+        <v>99382</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>136472417</v>
       </c>
       <c r="B98" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>136472419</v>
       </c>
       <c r="B99" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>136472413</v>
       </c>
       <c r="B119" t="n">
-        <v>98221</v>
+        <v>98227</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -2461,7 +2461,7 @@
         <v>136472418</v>
       </c>
       <c r="B17" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136472416</v>
       </c>
       <c r="B49" t="n">
-        <v>111657</v>
+        <v>111659</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>136472421</v>
       </c>
       <c r="B54" t="n">
-        <v>99382</v>
+        <v>99384</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>136472417</v>
       </c>
       <c r="B98" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>136472419</v>
       </c>
       <c r="B99" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>136472413</v>
       </c>
       <c r="B119" t="n">
-        <v>98227</v>
+        <v>98229</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -2461,7 +2461,7 @@
         <v>136472418</v>
       </c>
       <c r="B17" t="n">
-        <v>92528</v>
+        <v>92529</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>136472416</v>
       </c>
       <c r="B49" t="n">
-        <v>111659</v>
+        <v>111660</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6979,7 +6979,7 @@
         <v>136472421</v>
       </c>
       <c r="B54" t="n">
-        <v>99384</v>
+        <v>99385</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -12291,7 +12291,7 @@
         <v>136472417</v>
       </c>
       <c r="B98" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>136472419</v>
       </c>
       <c r="B99" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -14794,7 +14794,7 @@
         <v>136472413</v>
       </c>
       <c r="B119" t="n">
-        <v>98229</v>
+        <v>98230</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96799</v>
+        <v>96803</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87592</v>
+        <v>87596</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87478</v>
+        <v>87482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87478</v>
+        <v>87482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79550</v>
+        <v>79552</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79550</v>
+        <v>79552</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79550</v>
+        <v>79552</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92138</v>
+        <v>92142</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92466</v>
+        <v>92470</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96580</v>
+        <v>96584</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96703</v>
+        <v>96707</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87498</v>
+        <v>87502</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93458</v>
+        <v>93462</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111666</v>
+        <v>111670</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99391</v>
+        <v>99395</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99391</v>
+        <v>99395</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99391</v>
+        <v>99395</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99391</v>
+        <v>99395</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99391</v>
+        <v>99395</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99272</v>
+        <v>99276</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101578</v>
+        <v>101582</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98422</v>
+        <v>98426</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98422</v>
+        <v>98426</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106496</v>
+        <v>106500</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78487</v>
+        <v>78489</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96803</v>
+        <v>96805</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96584</v>
+        <v>96586</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96707</v>
+        <v>96709</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16575,7 +16575,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111670</v>
+        <v>111672</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99395</v>
+        <v>99397</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99395</v>
+        <v>99397</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99395</v>
+        <v>99397</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99395</v>
+        <v>99397</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99395</v>
+        <v>99397</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101582</v>
+        <v>101584</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98426</v>
+        <v>98428</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96805</v>
+        <v>96807</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87596</v>
+        <v>87598</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87482</v>
+        <v>87484</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87482</v>
+        <v>87484</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79552</v>
+        <v>79555</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79552</v>
+        <v>79555</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79552</v>
+        <v>79555</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92142</v>
+        <v>92144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
+          <t>Cajsa Björkén, Tomas Falk, Ingemar Södergren, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92470</v>
+        <v>92472</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96709</v>
+        <v>96711</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87502</v>
+        <v>87504</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93462</v>
+        <v>93464</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -14863,7 +14863,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
+          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16575,7 +16575,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111672</v>
+        <v>111674</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99397</v>
+        <v>99399</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99397</v>
+        <v>99399</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99397</v>
+        <v>99399</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99397</v>
+        <v>99399</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99397</v>
+        <v>99399</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99278</v>
+        <v>99280</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101584</v>
+        <v>101586</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98428</v>
+        <v>98430</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98428</v>
+        <v>98430</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106502</v>
+        <v>106504</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78489</v>
+        <v>78492</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96807</v>
+        <v>96820</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87598</v>
+        <v>87611</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87484</v>
+        <v>87497</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87484</v>
+        <v>87497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79555</v>
+        <v>79568</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79555</v>
+        <v>79568</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79555</v>
+        <v>79568</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92144</v>
+        <v>92157</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Cajsa Björkén, Tomas Falk, Ingemar Södergren, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92472</v>
+        <v>92485</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96588</v>
+        <v>96601</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96711</v>
+        <v>96724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87504</v>
+        <v>87517</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93464</v>
+        <v>93477</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>137125853</v>
       </c>
       <c r="B59" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>137125855</v>
       </c>
       <c r="B60" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>137125856</v>
       </c>
       <c r="B61" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>137125857</v>
       </c>
       <c r="B62" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>137125858</v>
       </c>
       <c r="B63" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>137125859</v>
       </c>
       <c r="B64" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>137125860</v>
       </c>
       <c r="B65" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>137125861</v>
       </c>
       <c r="B66" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>137125862</v>
       </c>
       <c r="B67" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>137125863</v>
       </c>
       <c r="B68" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>137125864</v>
       </c>
       <c r="B69" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137125865</v>
       </c>
       <c r="B70" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>137125866</v>
       </c>
       <c r="B71" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>137125867</v>
       </c>
       <c r="B72" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>137125868</v>
       </c>
       <c r="B73" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>137126399</v>
       </c>
       <c r="B74" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>137126408</v>
       </c>
       <c r="B75" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>137126409</v>
       </c>
       <c r="B76" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>137126414</v>
       </c>
       <c r="B77" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>137127206</v>
       </c>
       <c r="B78" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137127209</v>
       </c>
       <c r="B79" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>137127215</v>
       </c>
       <c r="B80" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>137125814</v>
       </c>
       <c r="B82" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10412,7 +10412,7 @@
         <v>137125807</v>
       </c>
       <c r="B84" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10636,7 +10636,7 @@
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -11241,7 +11241,7 @@
         <v>137126422</v>
       </c>
       <c r="B91" t="n">
-        <v>44210</v>
+        <v>44223</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>137127216</v>
       </c>
       <c r="B92" t="n">
-        <v>44210</v>
+        <v>44223</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13203,7 +13203,7 @@
         <v>137125791</v>
       </c>
       <c r="B107" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13310,7 +13310,7 @@
         <v>137125792</v>
       </c>
       <c r="B108" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14863,7 +14863,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14965,7 +14965,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15373,7 +15373,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15475,7 +15475,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15791,7 +15791,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16015,7 +16015,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16239,7 +16239,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Tomas Falk, Cajsa Björkén, Gillis Aronsson</t>
+          <t>Gillis Aronsson, Cajsa Björkén, Tomas Falk, Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
@@ -16575,7 +16575,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16808,7 +16808,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111674</v>
+        <v>111687</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17693,7 +17693,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99399</v>
+        <v>99412</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18253,7 +18253,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99280</v>
+        <v>99293</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23555,7 +23555,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23657,7 +23657,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23768,7 +23768,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23879,7 +23879,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23990,7 +23990,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24212,7 +24212,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24434,7 +24434,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24545,7 +24545,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24758,7 +24758,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24869,7 +24869,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25091,7 +25091,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25202,7 +25202,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25313,7 +25313,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25424,7 +25424,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25748,7 +25748,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25869,7 +25869,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26102,7 +26102,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26335,7 +26335,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26577,7 +26577,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26698,7 +26698,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26819,7 +26819,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29341,7 +29341,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29647,7 +29647,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29749,7 +29749,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29963,7 +29963,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30187,7 +30187,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30299,7 +30299,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30411,7 +30411,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35441,7 +35441,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35645,7 +35645,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35747,7 +35747,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35849,7 +35849,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35951,7 +35951,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36053,7 +36053,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36155,7 +36155,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36359,7 +36359,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36461,7 +36461,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36563,7 +36563,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36675,7 +36675,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36787,7 +36787,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101586</v>
+        <v>101599</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36899,7 +36899,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98430</v>
+        <v>98443</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37001,7 +37001,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98430</v>
+        <v>98443</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37234,7 +37234,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106504</v>
+        <v>106517</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37355,7 +37355,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78492</v>
+        <v>78505</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96820</v>
+        <v>96822</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87611</v>
+        <v>87613</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87497</v>
+        <v>87499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79568</v>
+        <v>79570</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79568</v>
+        <v>79570</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79568</v>
+        <v>79570</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92157</v>
+        <v>92159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92485</v>
+        <v>92487</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96724</v>
+        <v>96726</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87517</v>
+        <v>87519</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93477</v>
+        <v>93478</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>137125853</v>
       </c>
       <c r="B59" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>137125855</v>
       </c>
       <c r="B60" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>137125856</v>
       </c>
       <c r="B61" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>137125857</v>
       </c>
       <c r="B62" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>137125858</v>
       </c>
       <c r="B63" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>137125859</v>
       </c>
       <c r="B64" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>137125860</v>
       </c>
       <c r="B65" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>137125861</v>
       </c>
       <c r="B66" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>137125862</v>
       </c>
       <c r="B67" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>137125863</v>
       </c>
       <c r="B68" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>137125864</v>
       </c>
       <c r="B69" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137125865</v>
       </c>
       <c r="B70" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>137125866</v>
       </c>
       <c r="B71" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>137125867</v>
       </c>
       <c r="B72" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>137125868</v>
       </c>
       <c r="B73" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>137126399</v>
       </c>
       <c r="B74" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>137126408</v>
       </c>
       <c r="B75" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>137126409</v>
       </c>
       <c r="B76" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>137126414</v>
       </c>
       <c r="B77" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>137127206</v>
       </c>
       <c r="B78" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137127209</v>
       </c>
       <c r="B79" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>137127215</v>
       </c>
       <c r="B80" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>137125814</v>
       </c>
       <c r="B82" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10214,11 +10214,7 @@
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
@@ -10412,7 +10408,7 @@
         <v>137125807</v>
       </c>
       <c r="B84" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10438,11 +10434,7 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
@@ -10545,11 +10537,7 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sladdarön, SO om Öregrund, Upl</t>
@@ -11241,7 +11229,7 @@
         <v>137126422</v>
       </c>
       <c r="B91" t="n">
-        <v>44223</v>
+        <v>44225</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11267,11 +11255,7 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Sladdarön anmälan, Upl</t>
@@ -11358,7 +11342,7 @@
         <v>137127216</v>
       </c>
       <c r="B92" t="n">
-        <v>44223</v>
+        <v>44225</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13203,7 +13187,7 @@
         <v>137125791</v>
       </c>
       <c r="B107" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13229,11 +13213,7 @@
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
@@ -13310,7 +13290,7 @@
         <v>137125792</v>
       </c>
       <c r="B108" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13336,11 +13316,7 @@
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Sladdarön, Upl</t>
@@ -14089,7 +14065,7 @@
         <v>137127154</v>
       </c>
       <c r="B115" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14201,7 +14177,7 @@
         <v>137127217</v>
       </c>
       <c r="B116" t="n">
-        <v>8452</v>
+        <v>8453</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14863,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14965,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15067,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15169,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15271,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15373,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15475,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15577,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15679,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15791,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15903,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16015,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16127,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16239,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16351,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16463,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16575,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16696,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16808,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111687</v>
+        <v>111689</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17479,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17581,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17693,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17805,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17917,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99412</v>
+        <v>99414</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18253,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99293</v>
+        <v>99295</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23555,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23657,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23768,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23879,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23990,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24101,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24212,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24323,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24434,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24545,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24656,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24758,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24869,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24980,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25091,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25202,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25313,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25424,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25535,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25646,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25748,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25869,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25981,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26102,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26223,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26335,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26456,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26577,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26698,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26819,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29239,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29341,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29443,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29545,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29647,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29749,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29851,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29963,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30075,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30187,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30299,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30411,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35339,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35441,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35543,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35645,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35747,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35849,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35951,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36053,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36155,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36257,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36359,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36461,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36563,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36675,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36787,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101599</v>
+        <v>101601</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36899,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98443</v>
+        <v>98445</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37001,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98443</v>
+        <v>98445</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37234,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106517</v>
+        <v>106519</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37264,11 +37240,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+      <c r="K319" t="inlineStr"/>
       <c r="P319" t="inlineStr">
         <is>
           <t>Sladdarön, SO om Öregrund, Upl</t>
@@ -37355,7 +37327,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78505</v>
+        <v>78507</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96822</v>
+        <v>96825</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87613</v>
+        <v>87616</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87499</v>
+        <v>87502</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87499</v>
+        <v>87502</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92487</v>
+        <v>92490</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96603</v>
+        <v>96606</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96726</v>
+        <v>96729</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87519</v>
+        <v>87522</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93478</v>
+        <v>93481</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111689</v>
+        <v>111695</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99414</v>
+        <v>99417</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99295</v>
+        <v>99298</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101601</v>
+        <v>101604</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98445</v>
+        <v>98448</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98445</v>
+        <v>98448</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106519</v>
+        <v>106523</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96825</v>
+        <v>96835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87616</v>
+        <v>87626</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87502</v>
+        <v>87512</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87502</v>
+        <v>87512</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79570</v>
+        <v>79580</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79570</v>
+        <v>79580</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79570</v>
+        <v>79580</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92162</v>
+        <v>92172</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92490</v>
+        <v>92500</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96606</v>
+        <v>96616</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96729</v>
+        <v>96739</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87522</v>
+        <v>87532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93481</v>
+        <v>93491</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>137125853</v>
       </c>
       <c r="B59" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>137125855</v>
       </c>
       <c r="B60" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>137125856</v>
       </c>
       <c r="B61" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>137125857</v>
       </c>
       <c r="B62" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>137125858</v>
       </c>
       <c r="B63" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>137125859</v>
       </c>
       <c r="B64" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>137125860</v>
       </c>
       <c r="B65" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>137125861</v>
       </c>
       <c r="B66" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>137125862</v>
       </c>
       <c r="B67" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>137125863</v>
       </c>
       <c r="B68" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>137125864</v>
       </c>
       <c r="B69" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137125865</v>
       </c>
       <c r="B70" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>137125866</v>
       </c>
       <c r="B71" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>137125867</v>
       </c>
       <c r="B72" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>137125868</v>
       </c>
       <c r="B73" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>137126399</v>
       </c>
       <c r="B74" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>137126408</v>
       </c>
       <c r="B75" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>137126409</v>
       </c>
       <c r="B76" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>137126414</v>
       </c>
       <c r="B77" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>137127206</v>
       </c>
       <c r="B78" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137127209</v>
       </c>
       <c r="B79" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>137127215</v>
       </c>
       <c r="B80" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>137125814</v>
       </c>
       <c r="B82" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137125807</v>
       </c>
       <c r="B84" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10511,7 +10511,7 @@
         <v>137131469</v>
       </c>
       <c r="B85" t="n">
-        <v>4777</v>
+        <v>4783</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10771,7 +10771,7 @@
         <v>137125906</v>
       </c>
       <c r="B87" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10888,7 +10888,7 @@
         <v>137125907</v>
       </c>
       <c r="B88" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>137127190</v>
       </c>
       <c r="B89" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>137127205</v>
       </c>
       <c r="B90" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>137126422</v>
       </c>
       <c r="B91" t="n">
-        <v>44225</v>
+        <v>44235</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>137127216</v>
       </c>
       <c r="B92" t="n">
-        <v>44225</v>
+        <v>44235</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12490,7 +12490,7 @@
         <v>137125885</v>
       </c>
       <c r="B101" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>137125886</v>
       </c>
       <c r="B102" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>137125887</v>
       </c>
       <c r="B103" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>137125888</v>
       </c>
       <c r="B104" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12958,7 +12958,7 @@
         <v>137125889</v>
       </c>
       <c r="B105" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13075,7 +13075,7 @@
         <v>137127220</v>
       </c>
       <c r="B106" t="n">
-        <v>4783</v>
+        <v>4789</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>137125791</v>
       </c>
       <c r="B107" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>137125792</v>
       </c>
       <c r="B108" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>137127154</v>
       </c>
       <c r="B115" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>137127217</v>
       </c>
       <c r="B116" t="n">
-        <v>8453</v>
+        <v>8459</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111695</v>
+        <v>111717</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99417</v>
+        <v>99427</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99298</v>
+        <v>99308</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101604</v>
+        <v>101619</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98448</v>
+        <v>98458</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98448</v>
+        <v>98458</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106523</v>
+        <v>106543</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78507</v>
+        <v>78517</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96835</v>
+        <v>96836</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87626</v>
+        <v>87627</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87512</v>
+        <v>87513</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92172</v>
+        <v>92173</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92500</v>
+        <v>92501</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96739</v>
+        <v>96740</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93491</v>
+        <v>93492</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111717</v>
+        <v>111718</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99427</v>
+        <v>99428</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99308</v>
+        <v>99309</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101619</v>
+        <v>101620</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98458</v>
+        <v>98459</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98458</v>
+        <v>98459</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106543</v>
+        <v>106544</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96836</v>
+        <v>96841</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87627</v>
+        <v>87630</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87513</v>
+        <v>87516</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87513</v>
+        <v>87516</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79580</v>
+        <v>79583</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92173</v>
+        <v>92176</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92501</v>
+        <v>92504</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96617</v>
+        <v>96622</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96740</v>
+        <v>96745</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93492</v>
+        <v>93497</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>137125853</v>
       </c>
       <c r="B59" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>137125855</v>
       </c>
       <c r="B60" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>137125856</v>
       </c>
       <c r="B61" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>137125857</v>
       </c>
       <c r="B62" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>137125858</v>
       </c>
       <c r="B63" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>137125859</v>
       </c>
       <c r="B64" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>137125860</v>
       </c>
       <c r="B65" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>137125861</v>
       </c>
       <c r="B66" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>137125862</v>
       </c>
       <c r="B67" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>137125863</v>
       </c>
       <c r="B68" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>137125864</v>
       </c>
       <c r="B69" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137125865</v>
       </c>
       <c r="B70" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>137125866</v>
       </c>
       <c r="B71" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>137125867</v>
       </c>
       <c r="B72" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>137125868</v>
       </c>
       <c r="B73" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>137126399</v>
       </c>
       <c r="B74" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>137126408</v>
       </c>
       <c r="B75" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>137126409</v>
       </c>
       <c r="B76" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>137126414</v>
       </c>
       <c r="B77" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>137127206</v>
       </c>
       <c r="B78" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137127209</v>
       </c>
       <c r="B79" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>137127215</v>
       </c>
       <c r="B80" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>137125814</v>
       </c>
       <c r="B82" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137125807</v>
       </c>
       <c r="B84" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>137126422</v>
       </c>
       <c r="B91" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>137127216</v>
       </c>
       <c r="B92" t="n">
-        <v>44235</v>
+        <v>44236</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>137125791</v>
       </c>
       <c r="B107" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>137125792</v>
       </c>
       <c r="B108" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111718</v>
+        <v>111723</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99428</v>
+        <v>99433</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99309</v>
+        <v>99314</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101620</v>
+        <v>101625</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98459</v>
+        <v>98464</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98459</v>
+        <v>98464</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106544</v>
+        <v>106549</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78517</v>
+        <v>78520</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96841</v>
+        <v>96843</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92176</v>
+        <v>92178</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92504</v>
+        <v>92506</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96622</v>
+        <v>96624</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96745</v>
+        <v>96747</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93497</v>
+        <v>93499</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111723</v>
+        <v>111726</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99433</v>
+        <v>99435</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99314</v>
+        <v>99316</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101625</v>
+        <v>101628</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98464</v>
+        <v>98466</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98464</v>
+        <v>98466</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106549</v>
+        <v>106552</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96843</v>
+        <v>96849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87630</v>
+        <v>87635</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87516</v>
+        <v>87521</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87516</v>
+        <v>87521</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79583</v>
+        <v>79588</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92178</v>
+        <v>92183</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92506</v>
+        <v>92511</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96624</v>
+        <v>96630</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96747</v>
+        <v>96753</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87536</v>
+        <v>87541</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93499</v>
+        <v>93505</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>137125853</v>
       </c>
       <c r="B59" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>137125855</v>
       </c>
       <c r="B60" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>137125856</v>
       </c>
       <c r="B61" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>137125857</v>
       </c>
       <c r="B62" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>137125858</v>
       </c>
       <c r="B63" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>137125859</v>
       </c>
       <c r="B64" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>137125860</v>
       </c>
       <c r="B65" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>137125861</v>
       </c>
       <c r="B66" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>137125862</v>
       </c>
       <c r="B67" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>137125863</v>
       </c>
       <c r="B68" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>137125864</v>
       </c>
       <c r="B69" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137125865</v>
       </c>
       <c r="B70" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>137125866</v>
       </c>
       <c r="B71" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>137125867</v>
       </c>
       <c r="B72" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>137125868</v>
       </c>
       <c r="B73" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>137126399</v>
       </c>
       <c r="B74" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>137126408</v>
       </c>
       <c r="B75" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>137126409</v>
       </c>
       <c r="B76" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>137126414</v>
       </c>
       <c r="B77" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>137127206</v>
       </c>
       <c r="B78" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137127209</v>
       </c>
       <c r="B79" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>137127215</v>
       </c>
       <c r="B80" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>137125814</v>
       </c>
       <c r="B82" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137125807</v>
       </c>
       <c r="B84" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>137125791</v>
       </c>
       <c r="B107" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>137125792</v>
       </c>
       <c r="B108" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111726</v>
+        <v>111732</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99435</v>
+        <v>99441</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99316</v>
+        <v>99322</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101628</v>
+        <v>101634</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98466</v>
+        <v>98472</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98466</v>
+        <v>98472</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106552</v>
+        <v>106558</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78520</v>
+        <v>78525</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111732</v>
+        <v>111733</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106558</v>
+        <v>106559</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96849</v>
+        <v>96861</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87635</v>
+        <v>87646</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87521</v>
+        <v>87532</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87521</v>
+        <v>87532</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79588</v>
+        <v>79599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92183</v>
+        <v>92195</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92511</v>
+        <v>92523</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96630</v>
+        <v>96642</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96753</v>
+        <v>96765</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87541</v>
+        <v>87552</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93505</v>
+        <v>93517</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>137125853</v>
       </c>
       <c r="B59" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>137125855</v>
       </c>
       <c r="B60" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>137125856</v>
       </c>
       <c r="B61" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>137125857</v>
       </c>
       <c r="B62" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>137125858</v>
       </c>
       <c r="B63" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>137125859</v>
       </c>
       <c r="B64" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>137125860</v>
       </c>
       <c r="B65" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>137125861</v>
       </c>
       <c r="B66" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>137125862</v>
       </c>
       <c r="B67" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>137125863</v>
       </c>
       <c r="B68" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>137125864</v>
       </c>
       <c r="B69" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137125865</v>
       </c>
       <c r="B70" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>137125866</v>
       </c>
       <c r="B71" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>137125867</v>
       </c>
       <c r="B72" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>137125868</v>
       </c>
       <c r="B73" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>137126399</v>
       </c>
       <c r="B74" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>137126408</v>
       </c>
       <c r="B75" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>137126409</v>
       </c>
       <c r="B76" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>137126414</v>
       </c>
       <c r="B77" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>137127206</v>
       </c>
       <c r="B78" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137127209</v>
       </c>
       <c r="B79" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>137127215</v>
       </c>
       <c r="B80" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111733</v>
+        <v>111745</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99441</v>
+        <v>99453</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99322</v>
+        <v>99334</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101634</v>
+        <v>101646</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98472</v>
+        <v>98484</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98472</v>
+        <v>98484</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106559</v>
+        <v>106571</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78525</v>
+        <v>78536</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96861</v>
+        <v>96862</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87646</v>
+        <v>87647</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87532</v>
+        <v>87533</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79599</v>
+        <v>79600</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92195</v>
+        <v>92196</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92523</v>
+        <v>92524</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96642</v>
+        <v>96643</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96765</v>
+        <v>96766</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87552</v>
+        <v>87553</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93517</v>
+        <v>93518</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111745</v>
+        <v>111746</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99453</v>
+        <v>99454</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99334</v>
+        <v>99335</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101646</v>
+        <v>101647</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98484</v>
+        <v>98485</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98484</v>
+        <v>98485</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78536</v>
+        <v>78537</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96862</v>
+        <v>96865</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87647</v>
+        <v>87650</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87533</v>
+        <v>87536</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79600</v>
+        <v>79602</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92196</v>
+        <v>92199</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92524</v>
+        <v>92527</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96643</v>
+        <v>96646</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96766</v>
+        <v>96769</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87553</v>
+        <v>87556</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93518</v>
+        <v>93521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111746</v>
+        <v>111749</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99454</v>
+        <v>99457</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99335</v>
+        <v>99338</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101647</v>
+        <v>101650</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98485</v>
+        <v>98488</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98485</v>
+        <v>98488</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106572</v>
+        <v>106575</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78537</v>
+        <v>78539</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>

--- a/artfynd/A 28392-2026 artfynd.xlsx
+++ b/artfynd/A 28392-2026 artfynd.xlsx
@@ -965,7 +965,7 @@
         <v>137126381</v>
       </c>
       <c r="B4" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>137126384</v>
       </c>
       <c r="B5" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1189,7 +1189,7 @@
         <v>137126401</v>
       </c>
       <c r="B6" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>137126407</v>
       </c>
       <c r="B7" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         <v>137131476</v>
       </c>
       <c r="B8" t="n">
-        <v>97671</v>
+        <v>97675</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>137125880</v>
       </c>
       <c r="B9" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1657,7 +1657,7 @@
         <v>137125881</v>
       </c>
       <c r="B10" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>137125882</v>
       </c>
       <c r="B11" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>137127189</v>
       </c>
       <c r="B12" t="n">
-        <v>96865</v>
+        <v>96869</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,7 +1973,7 @@
         <v>137126400</v>
       </c>
       <c r="B13" t="n">
-        <v>87650</v>
+        <v>87654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,7 +2090,7 @@
         <v>137126416</v>
       </c>
       <c r="B14" t="n">
-        <v>87536</v>
+        <v>87540</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         <v>137127219</v>
       </c>
       <c r="B15" t="n">
-        <v>87536</v>
+        <v>87540</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2314,7 +2314,7 @@
         <v>137125812</v>
       </c>
       <c r="B16" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2448,7 +2448,7 @@
         <v>137126411</v>
       </c>
       <c r="B17" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>137127214</v>
       </c>
       <c r="B18" t="n">
-        <v>79602</v>
+        <v>79606</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>137126397</v>
       </c>
       <c r="B20" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2945,7 +2945,7 @@
         <v>137131466</v>
       </c>
       <c r="B21" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>137131470</v>
       </c>
       <c r="B22" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3217,7 +3217,7 @@
         <v>137131472</v>
       </c>
       <c r="B23" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3344,7 +3344,7 @@
         <v>137131473</v>
       </c>
       <c r="B24" t="n">
-        <v>92199</v>
+        <v>92203</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3612,7 +3612,7 @@
         <v>137127187</v>
       </c>
       <c r="B26" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3724,7 +3724,7 @@
         <v>137131471</v>
       </c>
       <c r="B27" t="n">
-        <v>92527</v>
+        <v>92531</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         <v>137125826</v>
       </c>
       <c r="B38" t="n">
-        <v>96646</v>
+        <v>96650</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>137125803</v>
       </c>
       <c r="B40" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
         <v>137125804</v>
       </c>
       <c r="B41" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>137125805</v>
       </c>
       <c r="B42" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>137125806</v>
       </c>
       <c r="B43" t="n">
-        <v>96769</v>
+        <v>96773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>137126418</v>
       </c>
       <c r="B44" t="n">
-        <v>87556</v>
+        <v>87560</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>137131465</v>
       </c>
       <c r="B46" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>137126415</v>
       </c>
       <c r="B47" t="n">
-        <v>93521</v>
+        <v>93525</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>137125853</v>
       </c>
       <c r="B59" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>137125855</v>
       </c>
       <c r="B60" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>137125856</v>
       </c>
       <c r="B61" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>137125857</v>
       </c>
       <c r="B62" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8005,7 +8005,7 @@
         <v>137125858</v>
       </c>
       <c r="B63" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8122,7 +8122,7 @@
         <v>137125859</v>
       </c>
       <c r="B64" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>137125860</v>
       </c>
       <c r="B65" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8356,7 +8356,7 @@
         <v>137125861</v>
       </c>
       <c r="B66" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>137125862</v>
       </c>
       <c r="B67" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8590,7 +8590,7 @@
         <v>137125863</v>
       </c>
       <c r="B68" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8707,7 +8707,7 @@
         <v>137125864</v>
       </c>
       <c r="B69" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>137125865</v>
       </c>
       <c r="B70" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8941,7 +8941,7 @@
         <v>137125866</v>
       </c>
       <c r="B71" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9058,7 +9058,7 @@
         <v>137125867</v>
       </c>
       <c r="B72" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>137125868</v>
       </c>
       <c r="B73" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9292,7 +9292,7 @@
         <v>137126399</v>
       </c>
       <c r="B74" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>137126408</v>
       </c>
       <c r="B75" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9516,7 +9516,7 @@
         <v>137126409</v>
       </c>
       <c r="B76" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>137126414</v>
       </c>
       <c r="B77" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9740,7 +9740,7 @@
         <v>137127206</v>
       </c>
       <c r="B78" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9852,7 +9852,7 @@
         <v>137127209</v>
       </c>
       <c r="B79" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9964,7 +9964,7 @@
         <v>137127215</v>
       </c>
       <c r="B80" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>137127211</v>
       </c>
       <c r="B81" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10188,7 +10188,7 @@
         <v>137125814</v>
       </c>
       <c r="B82" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10408,7 +10408,7 @@
         <v>137125807</v>
       </c>
       <c r="B84" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -13187,7 +13187,7 @@
         <v>137125791</v>
       </c>
       <c r="B107" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>137125792</v>
       </c>
       <c r="B108" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>137125794</v>
       </c>
       <c r="B122" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>137125795</v>
       </c>
       <c r="B123" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15043,7 +15043,7 @@
         <v>137125797</v>
       </c>
       <c r="B124" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15145,7 +15145,7 @@
         <v>137125798</v>
       </c>
       <c r="B125" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>137125799</v>
       </c>
       <c r="B126" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15349,7 +15349,7 @@
         <v>137125800</v>
       </c>
       <c r="B127" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>137125801</v>
       </c>
       <c r="B128" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15553,7 +15553,7 @@
         <v>137125802</v>
       </c>
       <c r="B129" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>137126390</v>
       </c>
       <c r="B130" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15767,7 +15767,7 @@
         <v>137126395</v>
       </c>
       <c r="B131" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>137127155</v>
       </c>
       <c r="B132" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15991,7 +15991,7 @@
         <v>137127157</v>
       </c>
       <c r="B133" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16103,7 +16103,7 @@
         <v>137127186</v>
       </c>
       <c r="B134" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>137127199</v>
       </c>
       <c r="B135" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>137127200</v>
       </c>
       <c r="B136" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>137131467</v>
       </c>
       <c r="B137" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16551,7 +16551,7 @@
         <v>137131480</v>
       </c>
       <c r="B138" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16672,7 +16672,7 @@
         <v>137131491</v>
       </c>
       <c r="B139" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>137131493</v>
       </c>
       <c r="B140" t="n">
-        <v>111749</v>
+        <v>111755</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17455,7 +17455,7 @@
         <v>137125813</v>
       </c>
       <c r="B146" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137126389</v>
       </c>
       <c r="B147" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137126391</v>
       </c>
       <c r="B148" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137126417</v>
       </c>
       <c r="B149" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137127197</v>
       </c>
       <c r="B150" t="n">
-        <v>99457</v>
+        <v>99461</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137126388</v>
       </c>
       <c r="B153" t="n">
-        <v>99338</v>
+        <v>99342</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -23531,7 +23531,7 @@
         <v>137125829</v>
       </c>
       <c r="B197" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>137125830</v>
       </c>
       <c r="B198" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23744,7 +23744,7 @@
         <v>137125831</v>
       </c>
       <c r="B199" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>137125832</v>
       </c>
       <c r="B200" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23966,7 +23966,7 @@
         <v>137125833</v>
       </c>
       <c r="B201" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -24077,7 +24077,7 @@
         <v>137125834</v>
       </c>
       <c r="B202" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -24188,7 +24188,7 @@
         <v>137125838</v>
       </c>
       <c r="B203" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>137125839</v>
       </c>
       <c r="B204" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -24410,7 +24410,7 @@
         <v>137125840</v>
       </c>
       <c r="B205" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>137125841</v>
       </c>
       <c r="B206" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -24632,7 +24632,7 @@
         <v>137125842</v>
       </c>
       <c r="B207" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>137125843</v>
       </c>
       <c r="B208" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>137125844</v>
       </c>
       <c r="B209" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>137125845</v>
       </c>
       <c r="B210" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -25067,7 +25067,7 @@
         <v>137125846</v>
       </c>
       <c r="B211" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -25178,7 +25178,7 @@
         <v>137125847</v>
       </c>
       <c r="B212" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>137125848</v>
       </c>
       <c r="B213" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -25400,7 +25400,7 @@
         <v>137125850</v>
       </c>
       <c r="B214" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>137125851</v>
       </c>
       <c r="B215" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -25622,7 +25622,7 @@
         <v>137125852</v>
       </c>
       <c r="B216" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>137126404</v>
       </c>
       <c r="B217" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -25845,7 +25845,7 @@
         <v>137127183</v>
       </c>
       <c r="B218" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25957,7 +25957,7 @@
         <v>137127185</v>
       </c>
       <c r="B219" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>137127188</v>
       </c>
       <c r="B220" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -26199,7 +26199,7 @@
         <v>137127192</v>
       </c>
       <c r="B221" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26311,7 +26311,7 @@
         <v>137127193</v>
       </c>
       <c r="B222" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>137127210</v>
       </c>
       <c r="B223" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>137127212</v>
       </c>
       <c r="B224" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26674,7 +26674,7 @@
         <v>137127213</v>
       </c>
       <c r="B225" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26795,7 +26795,7 @@
         <v>137131497</v>
       </c>
       <c r="B226" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>137125873</v>
       </c>
       <c r="B246" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>137125874</v>
       </c>
       <c r="B247" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>137125875</v>
       </c>
       <c r="B248" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29521,7 +29521,7 @@
         <v>137125876</v>
       </c>
       <c r="B249" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29623,7 +29623,7 @@
         <v>137125878</v>
       </c>
       <c r="B250" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>137125879</v>
       </c>
       <c r="B251" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>137126387</v>
       </c>
       <c r="B252" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29939,7 +29939,7 @@
         <v>137126413</v>
       </c>
       <c r="B253" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>137127191</v>
       </c>
       <c r="B254" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -30163,7 +30163,7 @@
         <v>137127203</v>
       </c>
       <c r="B255" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>137127222</v>
       </c>
       <c r="B256" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>137131486</v>
       </c>
       <c r="B257" t="n">
-        <v>106588</v>
+        <v>106594</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>137125911</v>
       </c>
       <c r="B301" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35417,7 +35417,7 @@
         <v>137125912</v>
       </c>
       <c r="B302" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35519,7 +35519,7 @@
         <v>137125913</v>
       </c>
       <c r="B303" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>137125914</v>
       </c>
       <c r="B304" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35723,7 +35723,7 @@
         <v>137125915</v>
       </c>
       <c r="B305" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>137125917</v>
       </c>
       <c r="B306" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35927,7 +35927,7 @@
         <v>137125918</v>
       </c>
       <c r="B307" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36029,7 +36029,7 @@
         <v>137125919</v>
       </c>
       <c r="B308" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>137125920</v>
       </c>
       <c r="B309" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -36233,7 +36233,7 @@
         <v>137125921</v>
       </c>
       <c r="B310" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36335,7 +36335,7 @@
         <v>137125922</v>
       </c>
       <c r="B311" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>137125924</v>
       </c>
       <c r="B312" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>137127196</v>
       </c>
       <c r="B313" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>137127208</v>
       </c>
       <c r="B314" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>137127221</v>
       </c>
       <c r="B315" t="n">
-        <v>101650</v>
+        <v>101654</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>137125824</v>
       </c>
       <c r="B316" t="n">
-        <v>98488</v>
+        <v>98492</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>137131477</v>
       </c>
       <c r="B317" t="n">
-        <v>98488</v>
+        <v>98492</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>137131485</v>
       </c>
       <c r="B319" t="n">
-        <v>106575</v>
+        <v>106581</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -37327,7 +37327,7 @@
         <v>137126412</v>
       </c>
       <c r="B320" t="n">
-        <v>78539</v>
+        <v>78543</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
